--- a/data/Type1/whole community/Reiss_2006a.xlsx
+++ b/data/Type1/whole community/Reiss_2006a.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bangoroffice365-my.sharepoint.com/personal/lrm22dyy_bangor_ac_uk/Documents/Desktop/DGENV thresholds request/Data/Type 1/whole community/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{6033E974-3CD0-4643-BE9E-B4C12761A3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91D34D4E-2B11-4105-8A2D-A37F17EAC57D}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{6033E974-3CD0-4643-BE9E-B4C12761A3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8304BEBB-A627-4016-A1C9-0961162193CA}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="36" windowWidth="19680" windowHeight="15792" activeTab="1" xr2:uid="{37C0102A-C8BF-4033-AC94-DE5EFFCCF06D}"/>
+    <workbookView xWindow="120" yWindow="36" windowWidth="19680" windowHeight="15792" firstSheet="1" activeTab="1" xr2:uid="{37C0102A-C8BF-4033-AC94-DE5EFFCCF06D}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata and protocols" sheetId="3" r:id="rId1"/>
@@ -94,6 +94,9 @@
     <t>outcome_units</t>
   </si>
   <si>
+    <t>total_abundance</t>
+  </si>
+  <si>
     <t>Reiss_2006a</t>
   </si>
   <si>
@@ -116,16 +119,13 @@
   </si>
   <si>
     <t>nr</t>
-  </si>
-  <si>
-    <t>total_abundance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,48 +615,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -989,110 +989,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A086968-53DB-4CA1-85AE-04CF43BF9F3E}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1105,9 +1105,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59F7124-4689-4D2B-B464-C2EDBD8B3363}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1142,12 +1145,12 @@
         <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>1990</v>
@@ -1159,13 +1162,13 @@
         <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>0.1</v>
@@ -1174,18 +1177,18 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2">
         <v>840.28992870000002</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1991</v>
@@ -1197,13 +1200,13 @@
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>0.1</v>
@@ -1212,18 +1215,18 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3">
         <v>235.869091</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1993</v>
@@ -1235,13 +1238,13 @@
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4">
         <v>0.1</v>
@@ -1250,18 +1253,18 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4">
         <v>11895.7014</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>1994</v>
@@ -1273,13 +1276,13 @@
         <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5">
         <v>0.1</v>
@@ -1288,18 +1291,18 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5">
         <v>530.86484849999999</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>1995</v>
@@ -1311,13 +1314,13 @@
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>0.1</v>
@@ -1326,18 +1329,18 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6">
         <v>967.60353399999997</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1996</v>
@@ -1349,13 +1352,13 @@
         <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7">
         <v>0.1</v>
@@ -1364,18 +1367,18 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>1953.965187</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1997</v>
@@ -1387,13 +1390,13 @@
         <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8">
         <v>0.1</v>
@@ -1402,18 +1405,18 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8">
         <v>4733.723868</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>1998</v>
@@ -1425,13 +1428,13 @@
         <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9">
         <v>0.1</v>
@@ -1440,18 +1443,18 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9">
         <v>3463.8428020000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -1463,13 +1466,13 @@
         <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10">
         <v>0.1</v>
@@ -1478,18 +1481,18 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10">
         <v>111.1393412</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>2001</v>
@@ -1501,13 +1504,13 @@
         <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11">
         <v>0.1</v>
@@ -1516,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11">
         <v>5812.6345259999998</v>
@@ -1536,9 +1539,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37B7224-4E19-481B-80FE-6CF48D4351EA}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1564,9 +1567,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>1990</v>
@@ -1575,24 +1578,24 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
       </c>
       <c r="G2">
         <v>840.28992870000002</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1991</v>
@@ -1601,24 +1604,24 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
       </c>
       <c r="G3">
         <v>235.869091</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1993</v>
@@ -1627,24 +1630,24 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
       </c>
       <c r="G4">
         <v>11895.7014</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>1994</v>
@@ -1653,24 +1656,24 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
       </c>
       <c r="G5">
         <v>530.86484849999999</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>1995</v>
@@ -1679,24 +1682,24 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
       </c>
       <c r="G6">
         <v>967.60353399999997</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1996</v>
@@ -1705,24 +1708,24 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
         <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
       </c>
       <c r="G7">
         <v>1953.965187</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1997</v>
@@ -1731,24 +1734,24 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
       </c>
       <c r="G8">
         <v>4733.723868</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>1998</v>
@@ -1757,24 +1760,24 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
       </c>
       <c r="G9">
         <v>3463.8428020000001</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -1783,24 +1786,24 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
       </c>
       <c r="G10">
         <v>111.1393412</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>2001</v>
@@ -1809,19 +1812,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
         <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
       </c>
       <c r="G11">
         <v>5812.6345259999998</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1839,6 +1842,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008C3347BB67BB9B48B9267C5825329A8D" ma:contentTypeVersion="" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="946ead2bedc6697490567b3bc7a69b8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f31fc9b1d39c82eedb31998474f3939">
     <xsd:element name="properties">
@@ -1952,44 +1964,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A55AFBB4-320A-400C-9D8C-AC02AB62F8FA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A55AFBB4-320A-400C-9D8C-AC02AB62F8FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C479573-092E-4452-A83E-B1F6FFE9022A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6505D574-9EEA-4439-AEDE-271BCD2CE81F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6505D574-9EEA-4439-AEDE-271BCD2CE81F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C479573-092E-4452-A83E-B1F6FFE9022A}"/>
 </file>